--- a/Result/profitability/7714.xlsx
+++ b/Result/profitability/7714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM15"/>
+  <dimension ref="A1:AM16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,6 +2335,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>584</v>
+      </c>
+      <c r="D16" t="n">
+        <v>484</v>
+      </c>
+      <c r="E16" t="n">
+        <v>99</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8.56%</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>62</v>
+      </c>
+      <c r="K16" t="n">
+        <v>51</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.70875</v>
+      </c>
+      <c r="N16" t="n">
+        <v>19.71625</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.5253164556962024</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.1144045761830473</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.8700000000000001</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.5649350649350651</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.689999999999998</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.09027777777777768</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
